--- a/other_doc/CROSS_II_config.xlsx
+++ b/other_doc/CROSS_II_config.xlsx
@@ -1,35 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\_工作相关\KPMG\CROSS II\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\KPMG\Solvency_Report_System\other_doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0CF477D-4716-4A60-B36C-04BECD5BCF18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28780" windowHeight="12160" activeTab="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="3" r:id="rId1"/>
     <sheet name="config" sheetId="1" r:id="rId2"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId3"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">config!$A$1:$N$93</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="11" r:id="rId4"/>
+    <pivotCache cacheId="27" r:id="rId3"/>
   </pivotCaches>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="256">
   <si>
     <t>公司</t>
   </si>
@@ -46,9 +55,6 @@
     <t>保存文件名</t>
   </si>
   <si>
-    <t>2024Q3</t>
-  </si>
-  <si>
     <t>https://www.newchinalife.com/info/53474</t>
   </si>
   <si>
@@ -412,10 +418,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>N</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>2024年3季度</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -701,9 +703,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
     <t>无法检查网页元素</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -797,14 +796,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>N</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>短时间内多次可能会下载失败，会被ban IP</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -849,10 +840,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>N</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>成功</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -885,10 +872,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>N</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>https://www.sinosig.com/v/pilu?type=sx&amp;tabIndex=10001_39</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -905,10 +888,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>N</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>横琴人寿</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -917,10 +896,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>N</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>国民养老</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -961,18 +936,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>N</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>农银人寿</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -981,10 +944,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>N</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>招商仁和</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1037,14 +996,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>N</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>东吴人寿</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1054,13 +1005,24 @@
   </si>
   <si>
     <t>成功</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025Q2</t>
+  </si>
+  <si>
+    <t>2025Q2</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1159,7 +1121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1169,14 +1131,12 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
@@ -1185,63 +1145,7 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <fill>
         <patternFill>
@@ -1290,31 +1194,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Summary"/>
-      <sheetName val="Check"/>
-      <sheetName val="Summary (2)"/>
-      <sheetName val="单位统一"/>
-      <sheetName val="From Python"/>
-      <sheetName val="十三精本季度"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="卢泉霖" refreshedDate="45663.443001041669" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="92">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="卢泉霖" refreshedDate="45663.443001041669" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="92" xr:uid="{00000000-000A-0000-FFFF-FFFF0B000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:M93" sheet="config"/>
   </cacheSource>
@@ -2851,7 +2732,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="数据透视表1" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="数据透视表1" cacheId="27" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField showAll="0"/>
@@ -3002,6 +2883,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
     </ext>
   </extLst>
 </pivotTableDefinition>
@@ -3291,7 +3175,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A3:B8"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3308,50 +3192,50 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="B3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="B4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="B3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="B4" s="10">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="B7">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="B5" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="B6" s="10">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="B7" s="10">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="B8" s="10">
+      <c r="B8">
         <v>92</v>
       </c>
     </row>
@@ -3362,8 +3246,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N93"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:M93"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="70.7265625" bestFit="1" customWidth="1"/>
@@ -3374,39 +3258,39 @@
     <col min="12" max="13" width="41.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J1" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>3</v>
@@ -3415,4350 +3299,3915 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>178</v>
+        <v>253</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E2" t="s">
-        <v>165</v>
-      </c>
-      <c r="F2" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F2" s="5"/>
       <c r="G2" s="2" t="str">
         <f>$J2&amp;"年第"&amp;$K2&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J2" s="5" t="str">
+        <v>255</v>
+      </c>
+      <c r="J2" t="str">
         <f t="shared" ref="J2:J33" si="0">LEFT(I2,4)</f>
-        <v>2024</v>
-      </c>
-      <c r="K2" s="5" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K2" t="str">
         <f t="shared" ref="K2:K33" si="1">RIGHT(I2,1)</f>
-        <v>3</v>
-      </c>
-      <c r="L2" s="5" t="str">
+        <v>2</v>
+      </c>
+      <c r="L2" t="str">
         <f>"D:\文档\_工作相关\KPMG\CROSS II\"&amp;I2</f>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M2" t="str">
         <f t="shared" ref="M2:M33" si="2">B2&amp;I2&amp;"偿付能力季度报告摘要.pdf"</f>
-        <v>平安寿险2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N2" t="e">
-        <f>COUNTIFS(#REF!,B2)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+        <v>平安寿险2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E3" t="s">
-        <v>165</v>
-      </c>
-      <c r="F3" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F3" s="5"/>
       <c r="G3" s="2" t="str">
         <f>$J3&amp;"年"&amp;$K3&amp;"季度"</f>
-        <v>2024年3季度</v>
+        <v>2025年2季度</v>
       </c>
       <c r="H3" s="2"/>
-      <c r="I3" t="str">
-        <f t="shared" ref="I3:I8" si="3">$I$2</f>
-        <v>2024Q3</v>
-      </c>
-      <c r="J3" s="5" t="str">
+      <c r="I3" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="J3" t="str">
         <f t="shared" si="0"/>
-        <v>2024</v>
-      </c>
-      <c r="K3" s="5" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K3" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L3" t="str">
-        <f t="shared" ref="L3:L34" si="4">$L$2</f>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" ref="L3:L34" si="3">$L$2</f>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M3" t="str">
         <f t="shared" si="2"/>
-        <v>中国人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N3" t="e">
-        <f>COUNTIFS(#REF!,B3)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+        <v>中国人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>165</v>
-      </c>
-      <c r="F4" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F4" s="5"/>
       <c r="G4" s="2" t="str">
         <f>$J4&amp;"年第"&amp;CHOOSE($K4,"一","二","三","四")&amp;"季度"</f>
-        <v>2024年第三季度</v>
+        <v>2025年第二季度</v>
       </c>
       <c r="H4" s="2"/>
-      <c r="I4" t="str">
+      <c r="I4" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J4" t="str">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
+      <c r="K4" t="str">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L4" t="str">
         <f t="shared" si="3"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J4" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>2024</v>
-      </c>
-      <c r="K4" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="L4" t="str">
-        <f t="shared" si="4"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M4" t="str">
         <f t="shared" si="2"/>
-        <v>新华保险2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N4" t="e">
-        <f>COUNTIFS(#REF!,B4)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+        <v>新华保险2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" t="s">
-        <v>165</v>
-      </c>
-      <c r="F5" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F5" s="5"/>
       <c r="G5" s="2" t="str">
         <f>$J5&amp;"年第"&amp;$K5&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H5" s="2"/>
-      <c r="I5" t="str">
+      <c r="I5" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J5" t="str">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
+      <c r="K5" t="str">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L5" t="str">
         <f t="shared" si="3"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J5" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>2024</v>
-      </c>
-      <c r="K5" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="L5" t="str">
-        <f t="shared" si="4"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M5" t="str">
         <f t="shared" si="2"/>
-        <v>太保寿险2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N5" t="e">
-        <f>COUNTIFS(#REF!,B5)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+        <v>太保寿险2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D6" t="s">
         <v>8</v>
       </c>
-      <c r="C6" t="s">
-        <v>184</v>
-      </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
       <c r="E6" t="s">
-        <v>165</v>
-      </c>
-      <c r="F6" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F6" s="5"/>
       <c r="G6" s="2" t="str">
         <f>$J6&amp;"年第"&amp;$K6&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H6" s="2"/>
-      <c r="I6" t="str">
+      <c r="I6" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J6" t="str">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
+      <c r="K6" t="str">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L6" t="str">
         <f t="shared" si="3"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J6" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>2024</v>
-      </c>
-      <c r="K6" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="L6" t="str">
-        <f t="shared" si="4"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M6" t="str">
         <f t="shared" si="2"/>
-        <v>招商信诺2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N6" t="e">
-        <f>COUNTIFS(#REF!,B6)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+        <v>招商信诺2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
-        <v>165</v>
-      </c>
-      <c r="F7" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F7" s="5"/>
       <c r="G7" s="2" t="str">
         <f>$J7&amp;"年第"&amp;$K7&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H7" s="2"/>
-      <c r="I7" t="str">
+      <c r="I7" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J7" t="str">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
+      <c r="K7" t="str">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L7" t="str">
         <f t="shared" si="3"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J7" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>2024</v>
-      </c>
-      <c r="K7" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="L7" t="str">
-        <f t="shared" si="4"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M7" t="str">
         <f t="shared" si="2"/>
-        <v>泰康人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N7" t="e">
-        <f>COUNTIFS(#REF!,B7)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+        <v>泰康人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D8" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E8" t="s">
-        <v>165</v>
-      </c>
-      <c r="F8" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F8" s="5"/>
       <c r="G8" s="2" t="str">
         <f>$J8&amp;"年第"&amp;$K8&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H8" s="4"/>
-      <c r="I8" t="str">
+      <c r="I8" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J8" t="str">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
+      <c r="K8" t="str">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L8" t="str">
         <f t="shared" si="3"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J8" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>2024</v>
-      </c>
-      <c r="K8" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="L8" t="str">
-        <f t="shared" si="4"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M8" t="str">
         <f t="shared" si="2"/>
-        <v>人保寿险2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N8" t="e">
-        <f>COUNTIFS(#REF!,B8)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+        <v>人保寿险2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
-        <v>165</v>
-      </c>
-      <c r="F9" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F9" s="5"/>
       <c r="G9" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H9" s="2"/>
-      <c r="I9" t="str">
-        <f t="shared" ref="I9:I40" si="5">$I$2</f>
-        <v>2024Q3</v>
-      </c>
-      <c r="J9" s="5" t="str">
+      <c r="I9" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J9" t="str">
         <f t="shared" si="0"/>
-        <v>2024</v>
-      </c>
-      <c r="K9" s="5" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K9" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L9" t="str">
-        <f t="shared" si="4"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="3"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M9" t="str">
         <f t="shared" si="2"/>
-        <v>中邮人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N9" t="e">
-        <f>COUNTIFS(#REF!,B9)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+        <v>中邮人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s">
-        <v>165</v>
-      </c>
-      <c r="F10" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F10" s="5"/>
       <c r="G10" s="2" t="str">
         <f>$J10&amp;"年第"&amp;CHOOSE($K10,"一","二","三","四")&amp;"季度"</f>
-        <v>2024年第三季度</v>
+        <v>2025年第二季度</v>
       </c>
       <c r="H10" s="2"/>
-      <c r="I10" t="str">
-        <f t="shared" si="5"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J10" s="5" t="str">
+      <c r="I10" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J10" t="str">
         <f t="shared" si="0"/>
-        <v>2024</v>
-      </c>
-      <c r="K10" s="5" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K10" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L10" t="str">
-        <f t="shared" si="4"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="3"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M10" t="str">
         <f t="shared" si="2"/>
-        <v>工银安盛2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N10" t="e">
-        <f>COUNTIFS(#REF!,B10)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+        <v>工银安盛2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E11" t="s">
-        <v>165</v>
-      </c>
-      <c r="F11" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F11" s="5"/>
       <c r="G11" s="2" t="str">
         <f>$J11&amp;"年"&amp;$K11&amp;"季度"</f>
-        <v>2024年3季度</v>
+        <v>2025年2季度</v>
       </c>
       <c r="H11" s="2"/>
-      <c r="I11" t="str">
-        <f t="shared" si="5"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J11" s="5" t="str">
+      <c r="I11" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J11" t="str">
         <f t="shared" si="0"/>
-        <v>2024</v>
-      </c>
-      <c r="K11" s="5" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K11" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L11" t="str">
-        <f t="shared" si="4"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="3"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M11" t="str">
         <f t="shared" si="2"/>
-        <v>国华人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N11" t="e">
-        <f>COUNTIFS(#REF!,B11)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+        <v>国华人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>165</v>
-      </c>
-      <c r="F12" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F12" s="5"/>
       <c r="G12" s="2" t="str">
         <f>$J12&amp;"年第"&amp;$K12&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H12" s="2"/>
-      <c r="I12" t="str">
-        <f t="shared" si="5"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J12" s="5" t="str">
+      <c r="I12" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J12" t="str">
         <f t="shared" si="0"/>
-        <v>2024</v>
-      </c>
-      <c r="K12" s="5" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K12" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L12" t="str">
-        <f t="shared" si="4"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="3"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M12" t="str">
         <f t="shared" si="2"/>
-        <v>信泰人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N12" t="e">
-        <f>COUNTIFS(#REF!,B12)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+        <v>信泰人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E13" t="s">
-        <v>165</v>
-      </c>
-      <c r="F13" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F13" s="5"/>
       <c r="G13" s="2" t="str">
         <f>$J13&amp;"年第"&amp;$K13&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H13" s="2"/>
-      <c r="I13" t="str">
-        <f t="shared" si="5"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J13" s="5" t="str">
+      <c r="I13" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J13" t="str">
         <f t="shared" si="0"/>
-        <v>2024</v>
-      </c>
-      <c r="K13" s="5" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K13" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L13" t="str">
-        <f t="shared" si="4"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="3"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M13" t="str">
         <f t="shared" si="2"/>
-        <v>建信人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N13" t="e">
-        <f>COUNTIFS(#REF!,B13)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+        <v>建信人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E14" t="s">
-        <v>165</v>
-      </c>
-      <c r="F14" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F14" s="5"/>
       <c r="G14" s="2" t="str">
         <f>$J14&amp;"年"&amp;$K14&amp;"季度"</f>
-        <v>2024年3季度</v>
+        <v>2025年2季度</v>
       </c>
       <c r="H14" s="2"/>
-      <c r="I14" t="str">
-        <f t="shared" si="5"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J14" s="5" t="str">
+      <c r="I14" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J14" t="str">
         <f t="shared" si="0"/>
-        <v>2024</v>
-      </c>
-      <c r="K14" s="5" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K14" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L14" t="str">
-        <f t="shared" si="4"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="3"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M14" t="str">
         <f t="shared" si="2"/>
-        <v>民生人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N14" t="e">
-        <f>COUNTIFS(#REF!,B14)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+        <v>民生人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E15" t="s">
-        <v>165</v>
-      </c>
-      <c r="F15" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F15" s="5"/>
       <c r="G15" s="2" t="str">
         <f>$I$2</f>
-        <v>2024Q3</v>
+        <v>2025Q2</v>
       </c>
       <c r="H15" s="2"/>
-      <c r="I15" t="str">
-        <f t="shared" si="5"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J15" s="5" t="str">
+      <c r="I15" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J15" t="str">
         <f t="shared" si="0"/>
-        <v>2024</v>
-      </c>
-      <c r="K15" s="5" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K15" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L15" t="str">
-        <f t="shared" si="4"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="3"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M15" t="str">
         <f t="shared" si="2"/>
-        <v>中宏人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N15" t="e">
-        <f>COUNTIFS(#REF!,B15)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+        <v>中宏人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E16" t="s">
-        <v>165</v>
-      </c>
-      <c r="F16" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F16" s="5"/>
       <c r="G16" s="2" t="str">
         <f>$J16&amp;"年第"&amp;$K16&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H16" s="2"/>
-      <c r="I16" t="str">
-        <f t="shared" si="5"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J16" s="5" t="str">
+      <c r="I16" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J16" t="str">
         <f t="shared" si="0"/>
-        <v>2024</v>
-      </c>
-      <c r="K16" s="5" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K16" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L16" t="str">
-        <f t="shared" si="4"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="3"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M16" t="str">
         <f t="shared" si="2"/>
-        <v>中英人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N16" t="e">
-        <f>COUNTIFS(#REF!,B16)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+        <v>中英人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C17" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D17" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E17" t="s">
-        <v>165</v>
-      </c>
-      <c r="F17" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F17" s="5"/>
       <c r="G17" s="2" t="str">
         <f>$J17&amp;"年"&amp;$K17&amp;"季度"</f>
-        <v>2024年3季度</v>
+        <v>2025年2季度</v>
       </c>
       <c r="H17" s="2"/>
-      <c r="I17" t="str">
-        <f t="shared" si="5"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J17" s="5" t="str">
+      <c r="I17" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J17" t="str">
         <f t="shared" si="0"/>
-        <v>2024</v>
-      </c>
-      <c r="K17" s="5" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K17" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L17" t="str">
-        <f t="shared" si="4"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="3"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M17" t="str">
         <f t="shared" si="2"/>
-        <v>中美联泰2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N17" t="e">
-        <f>COUNTIFS(#REF!,B17)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+        <v>中美联泰2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E18" t="s">
-        <v>165</v>
-      </c>
-      <c r="F18" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F18" s="5"/>
       <c r="G18" s="2" t="str">
         <f>$J18&amp;"年第"&amp;$K18&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H18" s="2"/>
-      <c r="I18" t="str">
-        <f t="shared" si="5"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J18" s="5" t="str">
+      <c r="I18" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J18" t="str">
         <f t="shared" si="0"/>
-        <v>2024</v>
-      </c>
-      <c r="K18" s="5" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K18" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L18" t="str">
-        <f t="shared" si="4"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="3"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M18" t="str">
         <f t="shared" si="2"/>
-        <v>中意人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N18" t="e">
-        <f>COUNTIFS(#REF!,B18)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+        <v>中意人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B19" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C19" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D19" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E19" t="s">
-        <v>165</v>
-      </c>
-      <c r="F19" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F19" s="5"/>
       <c r="G19" s="2" t="str">
         <f>$J19&amp;"年第"&amp;CHOOSE($K19,"一","二","三","四")&amp;"季度"</f>
-        <v>2024年第三季度</v>
+        <v>2025年第二季度</v>
       </c>
       <c r="H19" s="2"/>
-      <c r="I19" t="str">
-        <f t="shared" si="5"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J19" s="5" t="str">
+      <c r="I19" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J19" t="str">
         <f t="shared" si="0"/>
-        <v>2024</v>
-      </c>
-      <c r="K19" s="5" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K19" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L19" t="str">
-        <f t="shared" si="4"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="3"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M19" t="str">
         <f t="shared" si="2"/>
-        <v>长城人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N19" t="e">
-        <f>COUNTIFS(#REF!,B19)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+        <v>长城人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E20" t="s">
-        <v>165</v>
-      </c>
-      <c r="F20" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F20" s="5"/>
       <c r="G20" s="2" t="str">
         <f>$J20&amp;"年第"&amp;$K20&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H20" s="2"/>
-      <c r="I20" t="str">
-        <f t="shared" si="5"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J20" s="5" t="str">
+      <c r="I20" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J20" t="str">
         <f t="shared" si="0"/>
-        <v>2024</v>
-      </c>
-      <c r="K20" s="5" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K20" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L20" t="str">
-        <f t="shared" si="4"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="3"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M20" t="str">
         <f t="shared" si="2"/>
-        <v>幸福人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N20" t="e">
-        <f>COUNTIFS(#REF!,B20)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+        <v>幸福人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C21" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E21" t="s">
-        <v>165</v>
-      </c>
-      <c r="F21" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F21" s="5"/>
       <c r="G21" s="2" t="str">
         <f>$J21&amp;"年"&amp;$K21&amp;"季度"</f>
-        <v>2024年3季度</v>
+        <v>2025年2季度</v>
       </c>
       <c r="H21" s="2"/>
-      <c r="I21" t="str">
-        <f t="shared" si="5"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J21" s="5" t="str">
+      <c r="I21" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J21" t="str">
         <f t="shared" si="0"/>
-        <v>2024</v>
-      </c>
-      <c r="K21" s="5" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K21" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L21" t="str">
-        <f t="shared" si="4"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="3"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M21" t="str">
         <f t="shared" si="2"/>
-        <v>光大永明2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N21" t="e">
-        <f>COUNTIFS(#REF!,B21)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+        <v>光大永明2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B22" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C22" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E22" t="s">
-        <v>165</v>
-      </c>
-      <c r="F22" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F22" s="5"/>
       <c r="G22" s="2" t="str">
         <f>$J22&amp;"年"&amp;$K22&amp;"季度"</f>
-        <v>2024年3季度</v>
+        <v>2025年2季度</v>
       </c>
       <c r="H22" s="2"/>
-      <c r="I22" t="str">
-        <f t="shared" si="5"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J22" s="5" t="str">
+      <c r="I22" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J22" t="str">
         <f t="shared" si="0"/>
-        <v>2024</v>
-      </c>
-      <c r="K22" s="5" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K22" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L22" t="str">
-        <f t="shared" si="4"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="3"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M22" t="str">
         <f t="shared" si="2"/>
-        <v>英大人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N22" t="e">
-        <f>COUNTIFS(#REF!,B22)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+        <v>英大人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E23" t="s">
-        <v>165</v>
-      </c>
-      <c r="F23" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F23" s="5"/>
       <c r="G23" s="2" t="str">
         <f>$J23&amp;"年第"&amp;$K23&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H23" s="2"/>
-      <c r="I23" t="str">
-        <f t="shared" si="5"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J23" s="5" t="str">
+      <c r="I23" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J23" t="str">
         <f t="shared" si="0"/>
-        <v>2024</v>
-      </c>
-      <c r="K23" s="5" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K23" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L23" t="str">
-        <f t="shared" si="4"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="3"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M23" t="str">
         <f t="shared" si="2"/>
-        <v>同方全球2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N23" t="e">
-        <f>COUNTIFS(#REF!,B23)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+        <v>同方全球2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E24" t="s">
-        <v>165</v>
-      </c>
-      <c r="F24" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F24" s="5"/>
       <c r="G24" s="2" t="str">
         <f>$J24&amp;"年第"&amp;$K24&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H24" s="2"/>
-      <c r="I24" t="str">
-        <f t="shared" si="5"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J24" s="5" t="str">
+      <c r="I24" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J24" t="str">
         <f t="shared" si="0"/>
-        <v>2024</v>
-      </c>
-      <c r="K24" s="5" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K24" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L24" t="str">
-        <f t="shared" si="4"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="3"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M24" t="str">
         <f t="shared" si="2"/>
-        <v>中荷人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N24" t="e">
-        <f>COUNTIFS(#REF!,B24)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+        <v>中荷人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B25" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C25" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D25" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E25" t="s">
-        <v>165</v>
-      </c>
-      <c r="F25" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F25" s="5"/>
       <c r="G25" s="2" t="str">
         <f>$J25&amp;"年"&amp;$K25&amp;"季度"</f>
-        <v>2024年3季度</v>
+        <v>2025年2季度</v>
       </c>
       <c r="H25" s="2"/>
-      <c r="I25" t="str">
-        <f t="shared" si="5"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J25" s="5" t="str">
+      <c r="I25" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J25" t="str">
         <f t="shared" si="0"/>
-        <v>2024</v>
-      </c>
-      <c r="K25" s="5" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K25" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L25" t="str">
-        <f t="shared" si="4"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="3"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M25" t="str">
         <f t="shared" si="2"/>
-        <v>财信人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N25" t="e">
-        <f>COUNTIFS(#REF!,B25)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+        <v>财信人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B26" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C26" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D26" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E26" t="s">
-        <v>165</v>
-      </c>
-      <c r="F26" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F26" s="5"/>
       <c r="G26" s="2" t="str">
         <f>$J26&amp;"年第"&amp;CHOOSE($K26,"一","二","三","四")&amp;"季度"</f>
-        <v>2024年第三季度</v>
+        <v>2025年第二季度</v>
       </c>
       <c r="H26" s="2"/>
-      <c r="I26" t="str">
-        <f t="shared" si="5"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J26" s="5" t="str">
+      <c r="I26" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J26" t="str">
         <f t="shared" si="0"/>
-        <v>2024</v>
-      </c>
-      <c r="K26" s="5" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K26" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L26" t="str">
-        <f t="shared" si="4"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="3"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M26" t="str">
         <f t="shared" si="2"/>
-        <v>华泰人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N26" t="e">
-        <f>COUNTIFS(#REF!,B26)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+        <v>华泰人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B27" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C27" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D27" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E27" t="s">
-        <v>165</v>
-      </c>
-      <c r="F27" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F27" s="5"/>
       <c r="G27" s="2" t="str">
         <f>$J27&amp;"年第"&amp;$K27&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H27" s="2"/>
-      <c r="I27" t="str">
-        <f t="shared" si="5"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J27" s="5" t="str">
+      <c r="I27" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J27" t="str">
         <f t="shared" si="0"/>
-        <v>2024</v>
-      </c>
-      <c r="K27" s="5" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K27" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L27" t="str">
-        <f t="shared" si="4"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="3"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M27" t="str">
         <f t="shared" si="2"/>
-        <v>安联人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N27" t="e">
-        <f>COUNTIFS(#REF!,B27)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+        <v>安联人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B28" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C28" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E28" t="s">
-        <v>165</v>
-      </c>
-      <c r="F28" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F28" s="5"/>
       <c r="G28" s="2" t="str">
         <f>$J28&amp;"年"&amp;$K28&amp;"季度"</f>
-        <v>2024年3季度</v>
+        <v>2025年2季度</v>
       </c>
       <c r="H28" s="2"/>
-      <c r="I28" t="str">
-        <f t="shared" si="5"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J28" s="5" t="str">
+      <c r="I28" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J28" t="str">
         <f t="shared" si="0"/>
-        <v>2024</v>
-      </c>
-      <c r="K28" s="5" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K28" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L28" t="str">
-        <f t="shared" si="4"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="3"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M28" t="str">
         <f t="shared" si="2"/>
-        <v>北京人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N28" t="e">
-        <f>COUNTIFS(#REF!,B28)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+        <v>北京人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B29" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C29" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D29" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E29" t="s">
-        <v>165</v>
-      </c>
-      <c r="F29" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F29" s="5"/>
       <c r="G29" s="2" t="str">
         <f>$J29&amp;"年"&amp;$K29&amp;"季度"</f>
-        <v>2024年3季度</v>
+        <v>2025年2季度</v>
       </c>
       <c r="H29" s="2"/>
-      <c r="I29" t="str">
-        <f t="shared" si="5"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J29" s="5" t="str">
+      <c r="I29" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J29" t="str">
         <f t="shared" si="0"/>
-        <v>2024</v>
-      </c>
-      <c r="K29" s="5" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K29" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L29" t="str">
-        <f t="shared" si="4"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="3"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M29" t="str">
         <f t="shared" si="2"/>
-        <v>复星联合2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N29" t="e">
-        <f>COUNTIFS(#REF!,B29)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+        <v>复星联合2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" t="s">
+        <v>181</v>
+      </c>
+      <c r="D30" t="s">
         <v>73</v>
       </c>
-      <c r="C30" t="s">
-        <v>184</v>
-      </c>
-      <c r="D30" t="s">
-        <v>74</v>
-      </c>
       <c r="E30" t="s">
-        <v>165</v>
-      </c>
-      <c r="F30" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F30" s="5"/>
       <c r="G30" s="2" t="str">
         <f>$J30&amp;"年第"&amp;$K30&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H30" s="2"/>
-      <c r="I30" t="str">
-        <f t="shared" si="5"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J30" s="5" t="str">
+      <c r="I30" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J30" t="str">
         <f t="shared" si="0"/>
-        <v>2024</v>
-      </c>
-      <c r="K30" s="5" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K30" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L30" t="str">
-        <f t="shared" si="4"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="3"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M30" t="str">
         <f t="shared" si="2"/>
-        <v>国联人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N30" t="e">
-        <f>COUNTIFS(#REF!,B30)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+        <v>国联人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B31" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C31" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D31" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E31" t="s">
-        <v>165</v>
-      </c>
-      <c r="F31" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F31" s="5"/>
       <c r="G31" s="2" t="str">
         <f>$J31&amp;"年第"&amp;CHOOSE($K31,"一","二","三","四")&amp;"季度"</f>
-        <v>2024年第三季度</v>
+        <v>2025年第二季度</v>
       </c>
       <c r="H31" s="2"/>
-      <c r="I31" t="str">
-        <f t="shared" si="5"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J31" s="5" t="str">
+      <c r="I31" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J31" t="str">
         <f t="shared" si="0"/>
-        <v>2024</v>
-      </c>
-      <c r="K31" s="5" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K31" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L31" t="str">
-        <f t="shared" si="4"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="3"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M31" t="str">
         <f t="shared" si="2"/>
-        <v>信美人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N31" t="e">
-        <f>COUNTIFS(#REF!,B31)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+        <v>信美人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B32" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C32" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D32" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E32" t="s">
-        <v>165</v>
-      </c>
-      <c r="F32" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F32" s="5"/>
       <c r="G32" s="2" t="str">
         <f>$J32&amp;"年"&amp;CHOOSE($K32,"一","二","三","四")&amp;"季度"</f>
-        <v>2024年三季度</v>
+        <v>2025年二季度</v>
       </c>
       <c r="H32" s="2"/>
-      <c r="I32" t="str">
-        <f t="shared" si="5"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J32" s="5" t="str">
+      <c r="I32" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J32" t="str">
         <f t="shared" si="0"/>
-        <v>2024</v>
-      </c>
-      <c r="K32" s="5" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K32" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L32" t="str">
-        <f t="shared" si="4"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="3"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M32" t="str">
         <f t="shared" si="2"/>
-        <v>中华人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N32" t="e">
-        <f>COUNTIFS(#REF!,B32)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+        <v>中华人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B33" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C33" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D33" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E33" t="s">
-        <v>165</v>
-      </c>
-      <c r="F33" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F33" s="5"/>
       <c r="G33" s="2" t="str">
         <f>$J33&amp;"年"&amp;$K33&amp;"季度"</f>
-        <v>2024年3季度</v>
+        <v>2025年2季度</v>
       </c>
       <c r="H33" s="2"/>
-      <c r="I33" t="str">
-        <f t="shared" si="5"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J33" s="5" t="str">
+      <c r="I33" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J33" t="str">
         <f t="shared" si="0"/>
-        <v>2024</v>
-      </c>
-      <c r="K33" s="5" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K33" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L33" t="str">
-        <f t="shared" si="4"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="3"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M33" t="str">
         <f t="shared" si="2"/>
-        <v>复星保德信2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N33" t="e">
-        <f>COUNTIFS(#REF!,B33)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+        <v>复星保德信2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B34" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C34" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D34" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E34" t="s">
-        <v>165</v>
-      </c>
-      <c r="F34" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F34" s="5"/>
       <c r="G34" s="2" t="str">
         <f>$J34&amp;"年第"&amp;CHOOSE($K34,"一","二","三","四")&amp;"季度偿付能力"</f>
-        <v>2024年第三季度偿付能力</v>
+        <v>2025年第二季度偿付能力</v>
       </c>
       <c r="H34" s="2"/>
-      <c r="I34" t="str">
-        <f t="shared" si="5"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J34" s="5" t="str">
-        <f t="shared" ref="J34:J44" si="6">LEFT(I34,4)</f>
-        <v>2024</v>
-      </c>
-      <c r="K34" s="5" t="str">
-        <f t="shared" ref="K34:K44" si="7">RIGHT(I34,1)</f>
-        <v>3</v>
+      <c r="I34" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J34" t="str">
+        <f t="shared" ref="J34:J44" si="4">LEFT(I34,4)</f>
+        <v>2025</v>
+      </c>
+      <c r="K34" t="str">
+        <f t="shared" ref="K34:K44" si="5">RIGHT(I34,1)</f>
+        <v>2</v>
       </c>
       <c r="L34" t="str">
-        <f t="shared" si="4"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="3"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M34" t="str">
-        <f t="shared" ref="M34:M44" si="8">B34&amp;I34&amp;"偿付能力季度报告摘要.pdf"</f>
-        <v>汇丰人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N34" t="e">
-        <f>COUNTIFS(#REF!,B34)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+        <f t="shared" ref="M34:M44" si="6">B34&amp;I34&amp;"偿付能力季度报告摘要.pdf"</f>
+        <v>汇丰人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B35" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D35" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E35" t="s">
-        <v>165</v>
-      </c>
-      <c r="F35" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F35" s="5"/>
       <c r="G35" s="2" t="str">
         <f>$J35&amp;"年第"&amp;CHOOSE($K35,"一","二","三","四")&amp;"季度偿付能力"</f>
-        <v>2024年第三季度偿付能力</v>
+        <v>2025年第二季度偿付能力</v>
       </c>
       <c r="H35" s="2"/>
-      <c r="I35" t="str">
+      <c r="I35" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J35" t="str">
+        <f t="shared" si="4"/>
+        <v>2025</v>
+      </c>
+      <c r="K35" t="str">
         <f t="shared" si="5"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J35" s="5" t="str">
+        <v>2</v>
+      </c>
+      <c r="L35" t="str">
+        <f t="shared" ref="L35:L79" si="7">$L$2</f>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
+      </c>
+      <c r="M35" t="str">
         <f t="shared" si="6"/>
-        <v>2024</v>
-      </c>
-      <c r="K35" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="L35" t="str">
-        <f t="shared" ref="L35:L79" si="9">$L$2</f>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
-      </c>
-      <c r="M35" t="str">
-        <f t="shared" si="8"/>
-        <v>爱心人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N35" t="e">
-        <f>COUNTIFS(#REF!,B35)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+        <v>爱心人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B36" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C36" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D36" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E36" t="s">
-        <v>165</v>
-      </c>
-      <c r="F36" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F36" s="5"/>
       <c r="G36" s="2" t="str">
         <f>$J36&amp;"年第"&amp;$K36&amp;"季度偿付能力"</f>
-        <v>2024年第3季度偿付能力</v>
+        <v>2025年第2季度偿付能力</v>
       </c>
       <c r="H36" s="2"/>
-      <c r="I36" t="str">
+      <c r="I36" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J36" t="str">
+        <f t="shared" si="4"/>
+        <v>2025</v>
+      </c>
+      <c r="K36" t="str">
         <f t="shared" si="5"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J36" s="5" t="str">
+        <v>2</v>
+      </c>
+      <c r="L36" t="str">
+        <f t="shared" si="7"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
+      </c>
+      <c r="M36" t="str">
         <f t="shared" si="6"/>
-        <v>2024</v>
-      </c>
-      <c r="K36" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="L36" t="str">
-        <f t="shared" si="9"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
-      </c>
-      <c r="M36" t="str">
-        <f t="shared" si="8"/>
-        <v>小康人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N36" t="e">
-        <f>COUNTIFS(#REF!,B36)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+        <v>小康人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B37" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C37" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D37" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E37" t="s">
-        <v>165</v>
-      </c>
-      <c r="F37" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F37" s="5"/>
       <c r="G37" s="2" t="str">
         <f>$J37&amp;"年第"&amp;$K37&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H37" s="2"/>
-      <c r="I37" t="str">
+      <c r="I37" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J37" t="str">
+        <f t="shared" si="4"/>
+        <v>2025</v>
+      </c>
+      <c r="K37" t="str">
         <f t="shared" si="5"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J37" s="5" t="str">
+        <v>2</v>
+      </c>
+      <c r="L37" t="str">
+        <f t="shared" si="7"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
+      </c>
+      <c r="M37" t="str">
         <f t="shared" si="6"/>
-        <v>2024</v>
-      </c>
-      <c r="K37" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="L37" t="str">
-        <f t="shared" si="9"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
-      </c>
-      <c r="M37" t="str">
-        <f t="shared" si="8"/>
-        <v>北大方正2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N37" t="e">
-        <f>COUNTIFS(#REF!,B37)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+        <v>北大方正2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B38" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C38" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D38" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E38" t="s">
-        <v>165</v>
-      </c>
-      <c r="F38" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F38" s="5"/>
       <c r="G38" s="2" t="str">
         <f>$J38&amp;"年第"&amp;CHOOSE($K38,"一","二","三","四")&amp;"季度"</f>
-        <v>2024年第三季度</v>
+        <v>2025年第二季度</v>
       </c>
       <c r="H38" s="2"/>
-      <c r="I38" t="str">
+      <c r="I38" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J38" t="str">
+        <f t="shared" si="4"/>
+        <v>2025</v>
+      </c>
+      <c r="K38" t="str">
         <f t="shared" si="5"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J38" s="5" t="str">
+        <v>2</v>
+      </c>
+      <c r="L38" t="str">
+        <f t="shared" si="7"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
+      </c>
+      <c r="M38" t="str">
         <f t="shared" si="6"/>
-        <v>2024</v>
-      </c>
-      <c r="K38" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="L38" t="str">
-        <f t="shared" si="9"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
-      </c>
-      <c r="M38" t="str">
-        <f t="shared" si="8"/>
-        <v>瑞泰人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N38" t="e">
-        <f>COUNTIFS(#REF!,B38)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+        <v>瑞泰人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B39" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C39" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D39" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E39" t="s">
-        <v>165</v>
-      </c>
-      <c r="F39" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F39" s="5"/>
       <c r="G39" s="2" t="str">
         <f>$J39&amp;"年第"&amp;$K39&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H39" s="2"/>
-      <c r="I39" t="str">
+      <c r="I39" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J39" t="str">
+        <f t="shared" si="4"/>
+        <v>2025</v>
+      </c>
+      <c r="K39" t="str">
         <f t="shared" si="5"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J39" s="5" t="str">
+        <v>2</v>
+      </c>
+      <c r="L39" t="str">
+        <f t="shared" si="7"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
+      </c>
+      <c r="M39" t="str">
         <f t="shared" si="6"/>
-        <v>2024</v>
-      </c>
-      <c r="K39" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="L39" t="str">
-        <f t="shared" si="9"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
-      </c>
-      <c r="M39" t="str">
-        <f t="shared" si="8"/>
-        <v>国宝人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N39" t="e">
-        <f>COUNTIFS(#REF!,B39)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+        <v>国宝人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C40" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D40" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E40" t="s">
-        <v>165</v>
-      </c>
-      <c r="F40" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F40" s="5"/>
       <c r="G40" s="2" t="str">
         <f>$J40&amp;"年第"&amp;CHOOSE($K40,"一","二","三","四")&amp;"季度"</f>
-        <v>2024年第三季度</v>
+        <v>2025年第二季度</v>
       </c>
       <c r="H40" s="2"/>
-      <c r="I40" t="str">
+      <c r="I40" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J40" t="str">
+        <f t="shared" si="4"/>
+        <v>2025</v>
+      </c>
+      <c r="K40" t="str">
         <f t="shared" si="5"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J40" s="5" t="str">
+        <v>2</v>
+      </c>
+      <c r="L40" t="str">
+        <f t="shared" si="7"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
+      </c>
+      <c r="M40" t="str">
         <f t="shared" si="6"/>
-        <v>2024</v>
-      </c>
-      <c r="K40" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="L40" t="str">
-        <f t="shared" si="9"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
-      </c>
-      <c r="M40" t="str">
-        <f t="shared" si="8"/>
-        <v>和泰人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N40" t="e">
-        <f>COUNTIFS(#REF!,B40)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+        <v>和泰人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B41" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C41" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D41" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E41" t="s">
-        <v>165</v>
-      </c>
-      <c r="F41" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F41" s="5"/>
       <c r="G41" s="2" t="str">
         <f>$J41&amp;"年第"&amp;CHOOSE($K41,"一","二","三","四")&amp;"季度"</f>
-        <v>2024年第三季度</v>
+        <v>2025年第二季度</v>
       </c>
       <c r="H41" s="2"/>
-      <c r="I41" t="str">
-        <f t="shared" ref="I41:I90" si="10">$I$2</f>
-        <v>2024Q3</v>
-      </c>
-      <c r="J41" s="5" t="str">
+      <c r="I41" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J41" t="str">
+        <f t="shared" si="4"/>
+        <v>2025</v>
+      </c>
+      <c r="K41" t="str">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="L41" t="str">
+        <f t="shared" si="7"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
+      </c>
+      <c r="M41" t="str">
         <f t="shared" si="6"/>
-        <v>2024</v>
-      </c>
-      <c r="K41" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="L41" t="str">
-        <f t="shared" si="9"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
-      </c>
-      <c r="M41" t="str">
-        <f t="shared" si="8"/>
-        <v>国富人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N41" t="e">
-        <f>COUNTIFS(#REF!,B41)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+        <v>国富人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C42" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D42" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E42" t="s">
-        <v>165</v>
-      </c>
-      <c r="F42" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F42" s="5"/>
       <c r="G42" s="2" t="str">
         <f>$J42&amp;"年第"&amp;$K42&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H42" s="2"/>
-      <c r="I42" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J42" s="5" t="str">
+      <c r="I42" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J42" t="str">
+        <f t="shared" si="4"/>
+        <v>2025</v>
+      </c>
+      <c r="K42" t="str">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="L42" t="str">
+        <f t="shared" si="7"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
+      </c>
+      <c r="M42" t="str">
         <f t="shared" si="6"/>
-        <v>2024</v>
-      </c>
-      <c r="K42" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="L42" t="str">
-        <f t="shared" si="9"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
-      </c>
-      <c r="M42" t="str">
-        <f t="shared" si="8"/>
-        <v>华贵人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N42" t="e">
-        <f>COUNTIFS(#REF!,B42)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+        <v>华贵人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B43" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" t="s">
+        <v>181</v>
+      </c>
+      <c r="D43" t="s">
         <v>85</v>
       </c>
-      <c r="C43" t="s">
-        <v>184</v>
-      </c>
-      <c r="D43" t="s">
-        <v>86</v>
-      </c>
       <c r="E43" t="s">
-        <v>165</v>
-      </c>
-      <c r="F43" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F43" s="5"/>
       <c r="G43" s="2" t="str">
         <f>$J43&amp;"年第"&amp;$K43&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H43" s="2"/>
-      <c r="I43" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J43" s="5" t="str">
+      <c r="I43" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J43" t="str">
+        <f t="shared" si="4"/>
+        <v>2025</v>
+      </c>
+      <c r="K43" t="str">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="L43" t="str">
+        <f t="shared" si="7"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
+      </c>
+      <c r="M43" t="str">
         <f t="shared" si="6"/>
-        <v>2024</v>
-      </c>
-      <c r="K43" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="L43" t="str">
-        <f t="shared" si="9"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
-      </c>
-      <c r="M43" t="str">
-        <f t="shared" si="8"/>
-        <v>长生人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N43" t="e">
-        <f>COUNTIFS(#REF!,B43)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+        <v>长生人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B44" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C44" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E44" t="s">
-        <v>165</v>
-      </c>
-      <c r="F44" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F44" s="5"/>
       <c r="G44" s="2" t="str">
         <f>$J44&amp;"年第"&amp;$K44&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H44" s="2"/>
-      <c r="I44" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J44" s="5" t="str">
+      <c r="I44" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J44" t="str">
+        <f t="shared" si="4"/>
+        <v>2025</v>
+      </c>
+      <c r="K44" t="str">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="L44" t="str">
+        <f t="shared" si="7"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
+      </c>
+      <c r="M44" t="str">
         <f t="shared" si="6"/>
-        <v>2024</v>
-      </c>
-      <c r="K44" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="L44" t="str">
-        <f t="shared" si="9"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
-      </c>
-      <c r="M44" t="str">
-        <f t="shared" si="8"/>
-        <v>鼎诚人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N44" t="e">
-        <f>COUNTIFS(#REF!,B44)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+        <v>鼎诚人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B45" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C45" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D45" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E45" t="s">
-        <v>198</v>
-      </c>
-      <c r="F45" s="6"/>
+        <v>195</v>
+      </c>
+      <c r="F45" s="5"/>
       <c r="G45" s="2" t="str">
         <f>$J45&amp;"年第"&amp;$K45&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H45" s="2"/>
-      <c r="I45" t="str">
-        <f>config!$I$2</f>
-        <v>2024Q3</v>
-      </c>
-      <c r="J45" s="5" t="str">
-        <f t="shared" ref="J45:J64" si="11">LEFT(I45,4)</f>
-        <v>2024</v>
-      </c>
-      <c r="K45" s="5" t="str">
-        <f t="shared" ref="K45:K64" si="12">RIGHT(I45,1)</f>
-        <v>3</v>
+      <c r="I45" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J45" t="str">
+        <f t="shared" ref="J45:J64" si="8">LEFT(I45,4)</f>
+        <v>2025</v>
+      </c>
+      <c r="K45" t="str">
+        <f t="shared" ref="K45:K64" si="9">RIGHT(I45,1)</f>
+        <v>2</v>
       </c>
       <c r="L45" t="str">
         <f>config!$L$2</f>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M45" t="str">
-        <f t="shared" ref="M45:M53" si="13">B45&amp;I45&amp;"偿付能力季度报告摘要.pdf"</f>
-        <v>人保健康2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N45" t="e">
-        <f>COUNTIFS(#REF!,B45)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+        <f t="shared" ref="M45:M53" si="10">B45&amp;I45&amp;"偿付能力季度报告摘要.pdf"</f>
+        <v>人保健康2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B46" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C46" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D46" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E46" t="s">
-        <v>198</v>
-      </c>
-      <c r="F46" s="6"/>
+        <v>195</v>
+      </c>
+      <c r="F46" s="5"/>
       <c r="G46" s="2" t="str">
         <f>$J46&amp;"年第"&amp;CHOOSE($K46,"一","二","三","四")&amp;"季度"</f>
-        <v>2024年第三季度</v>
+        <v>2025年第二季度</v>
       </c>
       <c r="H46" s="2"/>
-      <c r="I46" t="str">
-        <f>config!$I$2</f>
-        <v>2024Q3</v>
-      </c>
-      <c r="J46" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>2024</v>
-      </c>
-      <c r="K46" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>3</v>
+      <c r="I46" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J46" t="str">
+        <f t="shared" si="8"/>
+        <v>2025</v>
+      </c>
+      <c r="K46" t="str">
+        <f t="shared" si="9"/>
+        <v>2</v>
       </c>
       <c r="L46" t="str">
         <f>config!$L$2</f>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M46" t="str">
-        <f t="shared" si="13"/>
-        <v>平安养老2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N46" t="e">
-        <f>COUNTIFS(#REF!,B46)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>平安养老2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B47" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C47" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D47" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E47" t="s">
-        <v>198</v>
-      </c>
-      <c r="F47" s="6"/>
+        <v>195</v>
+      </c>
+      <c r="F47" s="5"/>
       <c r="G47" s="2" t="str">
         <f>$J47&amp;"年第"&amp;$K47&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H47" s="2"/>
-      <c r="I47" t="str">
-        <f>config!$I$2</f>
-        <v>2024Q3</v>
-      </c>
-      <c r="J47" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>2024</v>
-      </c>
-      <c r="K47" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>3</v>
+      <c r="I47" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J47" t="str">
+        <f t="shared" si="8"/>
+        <v>2025</v>
+      </c>
+      <c r="K47" t="str">
+        <f t="shared" si="9"/>
+        <v>2</v>
       </c>
       <c r="L47" t="str">
         <f>config!$L$2</f>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M47" t="str">
-        <f t="shared" si="13"/>
-        <v>太保健康2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N47" t="e">
-        <f>COUNTIFS(#REF!,B47)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>太保健康2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B48" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C48" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D48" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="E48" t="s">
-        <v>165</v>
-      </c>
-      <c r="F48" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F48" s="5"/>
       <c r="G48" s="2" t="str">
         <f>$J48&amp;"年第"&amp;$K48&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H48" s="2"/>
-      <c r="I48" t="str">
-        <f>config!$I$2</f>
-        <v>2024Q3</v>
-      </c>
-      <c r="J48" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>2024</v>
-      </c>
-      <c r="K48" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>3</v>
+      <c r="I48" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J48" t="str">
+        <f t="shared" si="8"/>
+        <v>2025</v>
+      </c>
+      <c r="K48" t="str">
+        <f t="shared" si="9"/>
+        <v>2</v>
       </c>
       <c r="L48" t="str">
         <f>config!$L$2</f>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M48" t="str">
-        <f t="shared" si="13"/>
-        <v>泰康养老2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N48" t="e">
-        <f>COUNTIFS(#REF!,B48)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>泰康养老2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>101</v>
+      </c>
+      <c r="B49" t="s">
         <v>203</v>
       </c>
-      <c r="B49" t="s">
-        <v>208</v>
-      </c>
       <c r="C49" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D49" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E49" t="s">
-        <v>209</v>
-      </c>
-      <c r="F49" s="6"/>
+        <v>204</v>
+      </c>
+      <c r="F49" s="5"/>
       <c r="G49" s="2" t="str">
         <f>$J49&amp;"年第"&amp;$K49&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H49" s="2"/>
-      <c r="I49" t="str">
-        <f>config!$I$2</f>
-        <v>2024Q3</v>
-      </c>
-      <c r="J49" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>2024</v>
-      </c>
-      <c r="K49" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>3</v>
+      <c r="I49" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J49" t="str">
+        <f t="shared" si="8"/>
+        <v>2025</v>
+      </c>
+      <c r="K49" t="str">
+        <f t="shared" si="9"/>
+        <v>2</v>
       </c>
       <c r="L49" t="str">
         <f>config!$L$2</f>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M49" t="str">
-        <f t="shared" si="13"/>
-        <v>国寿养老2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N49" t="e">
-        <f>COUNTIFS(#REF!,B49)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>国寿养老2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>204</v>
+        <v>101</v>
       </c>
       <c r="B50" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C50" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D50" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E50" t="s">
-        <v>165</v>
-      </c>
-      <c r="F50" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F50" s="5"/>
       <c r="G50" s="2" t="str">
         <f>$J50&amp;"年"&amp;$K50&amp;"季度"</f>
-        <v>2024年3季度</v>
+        <v>2025年2季度</v>
       </c>
       <c r="H50" s="2"/>
-      <c r="I50" t="str">
-        <f>config!$I$2</f>
-        <v>2024Q3</v>
-      </c>
-      <c r="J50" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>2024</v>
-      </c>
-      <c r="K50" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>3</v>
+      <c r="I50" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J50" t="str">
+        <f t="shared" si="8"/>
+        <v>2025</v>
+      </c>
+      <c r="K50" t="str">
+        <f t="shared" si="9"/>
+        <v>2</v>
       </c>
       <c r="L50" t="str">
         <f>config!$L$2</f>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M50" t="str">
-        <f t="shared" si="13"/>
-        <v>新华养老2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N50" t="e">
-        <f>COUNTIFS(#REF!,B50)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>新华养老2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>204</v>
+        <v>101</v>
       </c>
       <c r="B51" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C51" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D51" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E51" t="s">
-        <v>165</v>
-      </c>
-      <c r="F51" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F51" s="5"/>
       <c r="G51" s="2" t="str">
         <f>$J51&amp;"年第"&amp;$K51&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H51" s="2"/>
-      <c r="I51" t="str">
-        <f>config!$I$2</f>
-        <v>2024Q3</v>
-      </c>
-      <c r="J51" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>2024</v>
-      </c>
-      <c r="K51" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>3</v>
+      <c r="I51" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J51" t="str">
+        <f t="shared" si="8"/>
+        <v>2025</v>
+      </c>
+      <c r="K51" t="str">
+        <f t="shared" si="9"/>
+        <v>2</v>
       </c>
       <c r="L51" t="str">
         <f>config!$L$2</f>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M51" t="str">
-        <f t="shared" si="13"/>
-        <v>人保养老2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N51" t="e">
-        <f>COUNTIFS(#REF!,B51)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>人保养老2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="B52" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C52" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D52" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E52" t="s">
-        <v>165</v>
-      </c>
-      <c r="F52" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F52" s="5"/>
       <c r="G52" s="2" t="str">
         <f>$J52&amp;"年第"&amp;$K52&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H52" s="2"/>
-      <c r="I52" t="str">
-        <f>config!$I$2</f>
-        <v>2024Q3</v>
-      </c>
-      <c r="J52" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>2024</v>
-      </c>
-      <c r="K52" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>3</v>
+      <c r="I52" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J52" t="str">
+        <f t="shared" si="8"/>
+        <v>2025</v>
+      </c>
+      <c r="K52" t="str">
+        <f t="shared" si="9"/>
+        <v>2</v>
       </c>
       <c r="L52" t="str">
         <f>config!$L$2</f>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M52" t="str">
-        <f t="shared" si="13"/>
-        <v>瑞华健康2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N52" t="e">
-        <f>COUNTIFS(#REF!,B52)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>瑞华健康2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>204</v>
+        <v>101</v>
       </c>
       <c r="B53" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C53" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D53" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="E53" t="s">
-        <v>165</v>
-      </c>
-      <c r="F53" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F53" s="5"/>
       <c r="G53" s="2" t="str">
         <f>$J53&amp;"年第"&amp;CHOOSE($K53,"一","二","三","四")&amp;"季度"</f>
-        <v>2024年第三季度</v>
+        <v>2025年第二季度</v>
       </c>
       <c r="H53" s="2"/>
-      <c r="I53" t="str">
-        <f>config!$I$2</f>
-        <v>2024Q3</v>
-      </c>
-      <c r="J53" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>2024</v>
-      </c>
-      <c r="K53" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>3</v>
+      <c r="I53" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J53" t="str">
+        <f t="shared" si="8"/>
+        <v>2025</v>
+      </c>
+      <c r="K53" t="str">
+        <f t="shared" si="9"/>
+        <v>2</v>
       </c>
       <c r="L53" t="str">
         <f>config!$L$2</f>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M53" t="str">
-        <f t="shared" si="13"/>
-        <v>恒安标准养老2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N53" t="e">
-        <f>COUNTIFS(#REF!,B53)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>恒安标准养老2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B54" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C54" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D54" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E54" t="s">
-        <v>217</v>
-      </c>
-      <c r="F54" s="6"/>
+        <v>211</v>
+      </c>
+      <c r="F54" s="5"/>
       <c r="G54" s="2" t="str">
         <f>$J54&amp;"年"&amp;$K54&amp;"季度"</f>
-        <v>2024年3季度</v>
+        <v>2025年2季度</v>
       </c>
       <c r="H54" s="2"/>
-      <c r="I54" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J54" s="5" t="str">
-        <f t="shared" ref="J54:J60" si="14">LEFT(I54,4)</f>
-        <v>2024</v>
-      </c>
-      <c r="K54" s="5" t="str">
-        <f t="shared" ref="K54:K60" si="15">RIGHT(I54,1)</f>
-        <v>3</v>
+      <c r="I54" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J54" t="str">
+        <f t="shared" ref="J54:J60" si="11">LEFT(I54,4)</f>
+        <v>2025</v>
+      </c>
+      <c r="K54" t="str">
+        <f t="shared" ref="K54:K60" si="12">RIGHT(I54,1)</f>
+        <v>2</v>
       </c>
       <c r="L54" t="str">
-        <f t="shared" si="9"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="7"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M54" t="str">
-        <f t="shared" ref="M54:M78" si="16">B54&amp;I54&amp;"偿付能力季度报告摘要.pdf"</f>
-        <v>弘康人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N54" t="e">
-        <f>COUNTIFS(#REF!,B54)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+        <f t="shared" ref="M54:M78" si="13">B54&amp;I54&amp;"偿付能力季度报告摘要.pdf"</f>
+        <v>弘康人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B55" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="C55" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D55" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="E55" t="s">
-        <v>165</v>
-      </c>
-      <c r="F55" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F55" s="5"/>
       <c r="G55" s="2" t="str">
         <f>$J55&amp;"年第"&amp;$K55&amp;"季度偿付能力"</f>
-        <v>2024年第3季度偿付能力</v>
+        <v>2025年第2季度偿付能力</v>
       </c>
       <c r="H55" s="2"/>
-      <c r="I55" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J55" s="5" t="str">
-        <f t="shared" si="14"/>
-        <v>2024</v>
-      </c>
-      <c r="K55" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>3</v>
+      <c r="I55" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J55" t="str">
+        <f t="shared" si="11"/>
+        <v>2025</v>
+      </c>
+      <c r="K55" t="str">
+        <f t="shared" si="12"/>
+        <v>2</v>
       </c>
       <c r="L55" t="str">
-        <f t="shared" si="9"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="7"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M55" t="str">
-        <f t="shared" si="16"/>
-        <v>德华安顾2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N55" t="e">
-        <f>COUNTIFS(#REF!,B55)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>德华安顾2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>225</v>
+        <v>101</v>
       </c>
       <c r="B56" t="s">
+        <v>214</v>
+      </c>
+      <c r="C56" t="s">
+        <v>181</v>
+      </c>
+      <c r="D56" t="s">
+        <v>219</v>
+      </c>
+      <c r="E56" t="s">
         <v>220</v>
       </c>
-      <c r="C56" t="s">
-        <v>184</v>
-      </c>
-      <c r="D56" t="s">
-        <v>226</v>
-      </c>
-      <c r="E56" t="s">
-        <v>227</v>
-      </c>
-      <c r="F56" s="6"/>
+      <c r="F56" s="5"/>
       <c r="G56" s="2" t="str">
         <f>$J56&amp;"年第"&amp;$K56&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H56" s="2"/>
-      <c r="I56" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J56" s="5" t="str">
-        <f t="shared" si="14"/>
-        <v>2024</v>
-      </c>
-      <c r="K56" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>3</v>
+      <c r="I56" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J56" t="str">
+        <f t="shared" si="11"/>
+        <v>2025</v>
+      </c>
+      <c r="K56" t="str">
+        <f t="shared" si="12"/>
+        <v>2</v>
       </c>
       <c r="L56" t="str">
-        <f t="shared" si="9"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="7"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M56" t="str">
-        <f t="shared" si="16"/>
-        <v>阳光人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N56" t="e">
-        <f>COUNTIFS(#REF!,B56)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>阳光人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B57" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C57" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D57" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="E57" t="s">
-        <v>229</v>
-      </c>
-      <c r="F57" s="6"/>
+        <v>222</v>
+      </c>
+      <c r="F57" s="5"/>
       <c r="G57" s="2" t="str">
         <f>$J57&amp;"年第"&amp;$K57&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H57" s="2"/>
-      <c r="I57" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J57" s="5" t="str">
-        <f t="shared" si="14"/>
-        <v>2024</v>
-      </c>
-      <c r="K57" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>3</v>
+      <c r="I57" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J57" t="str">
+        <f t="shared" si="11"/>
+        <v>2025</v>
+      </c>
+      <c r="K57" t="str">
+        <f t="shared" si="12"/>
+        <v>2</v>
       </c>
       <c r="L57" t="str">
-        <f t="shared" si="9"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="7"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M57" t="str">
-        <f t="shared" si="16"/>
-        <v>中银三星2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N57" t="e">
-        <f>COUNTIFS(#REF!,B57)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>中银三星2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>230</v>
+        <v>101</v>
       </c>
       <c r="B58" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="C58" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D58" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="E58" t="s">
-        <v>217</v>
-      </c>
-      <c r="F58" s="6"/>
+        <v>211</v>
+      </c>
+      <c r="F58" s="5"/>
       <c r="G58" s="2" t="str">
         <f>$J58&amp;"年第"&amp;$K58&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H58" s="2"/>
-      <c r="I58" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J58" s="5" t="str">
-        <f t="shared" si="14"/>
-        <v>2024</v>
-      </c>
-      <c r="K58" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>3</v>
+      <c r="I58" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J58" t="str">
+        <f t="shared" si="11"/>
+        <v>2025</v>
+      </c>
+      <c r="K58" t="str">
+        <f t="shared" si="12"/>
+        <v>2</v>
       </c>
       <c r="L58" t="str">
-        <f t="shared" si="9"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="7"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M58" t="str">
-        <f t="shared" si="16"/>
-        <v>横琴人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N58" t="e">
-        <f>COUNTIFS(#REF!,B58)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>横琴人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>233</v>
+        <v>101</v>
       </c>
       <c r="B59" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="C59" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D59" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E59" t="s">
-        <v>217</v>
-      </c>
-      <c r="F59" s="6"/>
+        <v>211</v>
+      </c>
+      <c r="F59" s="5"/>
       <c r="G59" s="2" t="str">
         <f>$J59&amp;"年第"&amp;CHOOSE($K59,"一","二","三","四")&amp;"季度"</f>
-        <v>2024年第三季度</v>
+        <v>2025年第二季度</v>
       </c>
       <c r="H59" s="2"/>
-      <c r="I59" t="str">
-        <f>config!$I$2</f>
-        <v>2024Q3</v>
-      </c>
-      <c r="J59" s="5" t="str">
-        <f t="shared" si="14"/>
-        <v>2024</v>
-      </c>
-      <c r="K59" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>3</v>
+      <c r="I59" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J59" t="str">
+        <f t="shared" si="11"/>
+        <v>2025</v>
+      </c>
+      <c r="K59" t="str">
+        <f t="shared" si="12"/>
+        <v>2</v>
       </c>
       <c r="L59" t="str">
         <f>config!$L$2</f>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M59" t="str">
-        <f t="shared" si="16"/>
-        <v>国民养老2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N59" t="e">
-        <f>COUNTIFS(#REF!,B59)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>国民养老2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B60" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="C60" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D60" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="E60" t="s">
-        <v>165</v>
-      </c>
-      <c r="F60" s="6"/>
+        <v>163</v>
+      </c>
+      <c r="F60" s="5"/>
       <c r="G60" s="2" t="str">
         <f>$J60&amp;"年"&amp;$K60&amp;"季度"</f>
-        <v>2024年3季度</v>
+        <v>2025年2季度</v>
       </c>
       <c r="H60" s="2"/>
-      <c r="I60" t="str">
-        <f>config!$I$2</f>
-        <v>2024Q3</v>
-      </c>
-      <c r="J60" s="5" t="str">
-        <f t="shared" si="14"/>
-        <v>2024</v>
-      </c>
-      <c r="K60" s="5" t="str">
-        <f t="shared" si="15"/>
-        <v>3</v>
+      <c r="I60" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J60" t="str">
+        <f t="shared" si="11"/>
+        <v>2025</v>
+      </c>
+      <c r="K60" t="str">
+        <f t="shared" si="12"/>
+        <v>2</v>
       </c>
       <c r="L60" t="str">
         <f>config!$L$2</f>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M60" t="str">
-        <f t="shared" si="16"/>
-        <v>平安健康2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N60" t="e">
-        <f>COUNTIFS(#REF!,B60)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>平安健康2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B61" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C61" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D61" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="E61" t="s">
-        <v>239</v>
-      </c>
-      <c r="F61" s="6"/>
+        <v>230</v>
+      </c>
+      <c r="F61" s="5"/>
       <c r="G61" s="2" t="str">
         <f>$J61&amp;"年"&amp;$K61&amp;"季度"</f>
-        <v>2024年3季度</v>
+        <v>2025年2季度</v>
       </c>
       <c r="H61" s="2"/>
-      <c r="I61" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J61" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>2024</v>
-      </c>
-      <c r="K61" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>3</v>
+      <c r="I61" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J61" t="str">
+        <f t="shared" si="8"/>
+        <v>2025</v>
+      </c>
+      <c r="K61" t="str">
+        <f t="shared" si="9"/>
+        <v>2</v>
       </c>
       <c r="L61" t="str">
-        <f t="shared" si="9"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="7"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M61" t="str">
-        <f t="shared" si="16"/>
-        <v>海保人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N61" t="e">
-        <f>COUNTIFS(#REF!,B61)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>海保人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>264</v>
+        <v>101</v>
       </c>
       <c r="B62" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="C62" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D62" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="E62" t="s">
-        <v>267</v>
-      </c>
-      <c r="F62" s="6"/>
+        <v>252</v>
+      </c>
+      <c r="F62" s="5"/>
       <c r="G62" s="2" t="str">
         <f>$J62&amp;"年第"&amp;CHOOSE($K62,"一","二","三","四")&amp;"季度"</f>
-        <v>2024年第三季度</v>
+        <v>2025年第二季度</v>
       </c>
       <c r="H62" s="2"/>
-      <c r="I62" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J62" s="5" t="str">
+      <c r="I62" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J62" t="str">
         <f>LEFT(I62,4)</f>
-        <v>2024</v>
-      </c>
-      <c r="K62" s="5" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K62" t="str">
         <f>RIGHT(I62,1)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L62" t="str">
-        <f t="shared" si="9"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="7"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M62" t="str">
-        <f t="shared" si="16"/>
-        <v>东吴人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N62" t="e">
-        <f>COUNTIFS(#REF!,B62)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>东吴人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B63" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C63" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D63" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E63" t="s">
-        <v>165</v>
-      </c>
-      <c r="F63" s="6" t="s">
-        <v>181</v>
+        <v>163</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>178</v>
       </c>
       <c r="G63" s="2" t="str">
         <f>$J63&amp;"年第"&amp;$K63&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H63" s="2"/>
-      <c r="I63" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J63" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>2024</v>
-      </c>
-      <c r="K63" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>3</v>
+      <c r="I63" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J63" t="str">
+        <f t="shared" si="8"/>
+        <v>2025</v>
+      </c>
+      <c r="K63" t="str">
+        <f t="shared" si="9"/>
+        <v>2</v>
       </c>
       <c r="L63" t="str">
-        <f t="shared" si="9"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="7"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M63" t="str">
-        <f t="shared" si="16"/>
-        <v>交银人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N63" t="e">
-        <f>COUNTIFS(#REF!,B63)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>交银人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>246</v>
+        <v>101</v>
       </c>
       <c r="B64" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="C64" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D64" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="E64" t="s">
-        <v>165</v>
-      </c>
-      <c r="F64" s="6" t="s">
-        <v>181</v>
+        <v>163</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>178</v>
       </c>
       <c r="G64" s="2" t="str">
         <f>$J64&amp;"年"&amp;$K64&amp;"季度"</f>
-        <v>2024年3季度</v>
+        <v>2025年2季度</v>
       </c>
       <c r="H64" s="2"/>
-      <c r="I64" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J64" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>2024</v>
-      </c>
-      <c r="K64" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v>3</v>
+      <c r="I64" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J64" t="str">
+        <f t="shared" si="8"/>
+        <v>2025</v>
+      </c>
+      <c r="K64" t="str">
+        <f t="shared" si="9"/>
+        <v>2</v>
       </c>
       <c r="L64" t="str">
-        <f t="shared" si="9"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="7"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M64" t="str">
-        <f t="shared" si="16"/>
-        <v>农银人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N64" t="e">
-        <f>COUNTIFS(#REF!,B64)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>农银人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>249</v>
+        <v>101</v>
       </c>
       <c r="B65" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="C65" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D65" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E65" t="s">
-        <v>251</v>
-      </c>
-      <c r="F65" s="6" t="s">
-        <v>205</v>
+        <v>238</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>200</v>
       </c>
       <c r="G65" s="2" t="str">
         <f>$J65&amp;"年第"&amp;$K65&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H65" s="2"/>
-      <c r="I65" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J65" s="5" t="str">
-        <f t="shared" ref="J65:J78" si="17">LEFT(I65,4)</f>
-        <v>2024</v>
-      </c>
-      <c r="K65" s="5" t="str">
-        <f t="shared" ref="K65:K78" si="18">RIGHT(I65,1)</f>
-        <v>3</v>
+      <c r="I65" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J65" t="str">
+        <f t="shared" ref="J65:J78" si="14">LEFT(I65,4)</f>
+        <v>2025</v>
+      </c>
+      <c r="K65" t="str">
+        <f t="shared" ref="K65:K78" si="15">RIGHT(I65,1)</f>
+        <v>2</v>
       </c>
       <c r="L65" t="str">
-        <f t="shared" si="9"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="7"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M65" t="str">
-        <f t="shared" si="16"/>
-        <v>招商仁和2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N65" t="e">
-        <f>COUNTIFS(#REF!,B65)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>招商仁和2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B66" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="C66" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D66" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="E66" t="s">
-        <v>165</v>
-      </c>
-      <c r="F66" s="6" t="s">
-        <v>205</v>
+        <v>163</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>200</v>
       </c>
       <c r="G66" s="2" t="str">
         <f>$J66&amp;"年第"&amp;$K66&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H66" s="2"/>
-      <c r="I66" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J66" s="5" t="str">
-        <f t="shared" si="17"/>
-        <v>2024</v>
-      </c>
-      <c r="K66" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>3</v>
+      <c r="I66" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J66" t="str">
+        <f t="shared" si="14"/>
+        <v>2025</v>
+      </c>
+      <c r="K66" t="str">
+        <f t="shared" si="15"/>
+        <v>2</v>
       </c>
       <c r="L66" t="str">
-        <f t="shared" si="9"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="7"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M66" t="str">
-        <f t="shared" si="16"/>
-        <v>华汇人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N66" t="e">
-        <f>COUNTIFS(#REF!,B66)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A67" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="B67" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="C67" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="D67" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="E67" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="F67" s="14" t="s">
-        <v>240</v>
+        <f t="shared" si="13"/>
+        <v>华汇人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>101</v>
+      </c>
+      <c r="B67" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="D67" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E67" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="F67" s="12" t="s">
+        <v>231</v>
       </c>
       <c r="G67" s="2" t="str">
         <f>$J67&amp;"年第"&amp;$K67&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H67" s="2"/>
-      <c r="I67" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J67" s="5" t="str">
-        <f t="shared" si="17"/>
-        <v>2024</v>
-      </c>
-      <c r="K67" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>3</v>
+      <c r="I67" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J67" t="str">
+        <f t="shared" si="14"/>
+        <v>2025</v>
+      </c>
+      <c r="K67" t="str">
+        <f t="shared" si="15"/>
+        <v>2</v>
       </c>
       <c r="L67" t="str">
-        <f t="shared" si="9"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="7"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M67" t="str">
-        <f t="shared" si="16"/>
-        <v>陆家嘴国泰2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N67" t="e">
-        <f>COUNTIFS(#REF!,B67)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A68" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="B68" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="C68" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="D68" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="E68" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="F68" s="14" t="s">
-        <v>240</v>
+        <f t="shared" si="13"/>
+        <v>陆家嘴国泰2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>101</v>
+      </c>
+      <c r="B68" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="D68" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="E68" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="F68" s="12" t="s">
+        <v>231</v>
       </c>
       <c r="G68" s="2" t="str">
         <f>$J68&amp;"年第"&amp;$K68&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H68" s="2"/>
-      <c r="I68" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J68" s="5" t="str">
-        <f t="shared" si="17"/>
-        <v>2024</v>
-      </c>
-      <c r="K68" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>3</v>
+      <c r="I68" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J68" t="str">
+        <f t="shared" si="14"/>
+        <v>2025</v>
+      </c>
+      <c r="K68" t="str">
+        <f t="shared" si="15"/>
+        <v>2</v>
       </c>
       <c r="L68" t="str">
-        <f t="shared" si="9"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="7"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M68" t="str">
-        <f t="shared" si="16"/>
-        <v>恒安标准2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N68" t="e">
-        <f>COUNTIFS(#REF!,B68)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A69" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="B69" s="13" t="s">
+        <f t="shared" si="13"/>
+        <v>恒安标准2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>101</v>
+      </c>
+      <c r="B69" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="D69" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="C69" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="D69" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E69" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="F69" s="14" t="s">
+      <c r="E69" s="11" t="s">
         <v>242</v>
+      </c>
+      <c r="F69" s="12" t="s">
+        <v>233</v>
       </c>
       <c r="G69" s="2" t="str">
         <f>"摘要"&amp;$J69&amp;"年第"&amp;$K69&amp;"季度"</f>
-        <v>摘要2024年第3季度</v>
+        <v>摘要2025年第2季度</v>
       </c>
       <c r="H69" s="2"/>
-      <c r="I69" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J69" s="5" t="str">
-        <f t="shared" si="17"/>
-        <v>2024</v>
-      </c>
-      <c r="K69" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>3</v>
+      <c r="I69" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J69" t="str">
+        <f t="shared" si="14"/>
+        <v>2025</v>
+      </c>
+      <c r="K69" t="str">
+        <f t="shared" si="15"/>
+        <v>2</v>
       </c>
       <c r="L69" t="str">
-        <f t="shared" si="9"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="7"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M69" t="str">
-        <f t="shared" si="16"/>
-        <v>三峡人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N69" t="e">
-        <f>COUNTIFS(#REF!,B69)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A70" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="B70" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="C70" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="D70" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="E70" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="F70" s="14" t="s">
-        <v>243</v>
+        <f t="shared" si="13"/>
+        <v>三峡人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>101</v>
+      </c>
+      <c r="B70" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E70" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="F70" s="12" t="s">
+        <v>234</v>
       </c>
       <c r="G70" s="2" t="str">
         <f>$J70&amp;"年第"&amp;$K70&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H70" s="2"/>
-      <c r="I70" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J70" s="5" t="str">
-        <f t="shared" si="17"/>
-        <v>2024</v>
-      </c>
-      <c r="K70" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>3</v>
+      <c r="I70" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J70" t="str">
+        <f t="shared" si="14"/>
+        <v>2025</v>
+      </c>
+      <c r="K70" t="str">
+        <f t="shared" si="15"/>
+        <v>2</v>
       </c>
       <c r="L70" t="str">
-        <f t="shared" si="9"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="7"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M70" t="str">
-        <f t="shared" si="16"/>
-        <v>中信保诚2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N70" t="e">
-        <f>COUNTIFS(#REF!,B70)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A71" s="13" t="s">
+        <f t="shared" si="13"/>
+        <v>中信保诚2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>101</v>
+      </c>
+      <c r="B71" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="D71" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="B71" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="C71" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="D71" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="E71" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="F71" s="14" t="s">
-        <v>258</v>
+      <c r="E71" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="F71" s="12" t="s">
+        <v>245</v>
       </c>
       <c r="G71" s="2" t="str">
         <f>$J71&amp;"年"&amp;CHOOSE($K71,"一","二","三","四")&amp;"季度"</f>
-        <v>2024年三季度</v>
+        <v>2025年二季度</v>
       </c>
       <c r="H71" s="2"/>
-      <c r="I71" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J71" s="5" t="str">
-        <f t="shared" si="17"/>
-        <v>2024</v>
-      </c>
-      <c r="K71" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>3</v>
+      <c r="I71" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J71" t="str">
+        <f t="shared" si="14"/>
+        <v>2025</v>
+      </c>
+      <c r="K71" t="str">
+        <f t="shared" si="15"/>
+        <v>2</v>
       </c>
       <c r="L71" t="str">
-        <f t="shared" si="9"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="7"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M71" t="str">
-        <f t="shared" si="16"/>
-        <v>利安人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N71" t="e">
-        <f>COUNTIFS(#REF!,B71)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A72" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="B72" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="C72" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="D72" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="E72" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="F72" s="14" t="s">
-        <v>259</v>
+        <f t="shared" si="13"/>
+        <v>利安人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>101</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="D72" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="E72" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="F72" s="12" t="s">
+        <v>246</v>
       </c>
       <c r="G72" s="2" t="str">
         <f>$J72&amp;"年第"&amp;CHOOSE($K72,"一","二","三","四")&amp;"季度"</f>
-        <v>2024年第三季度</v>
+        <v>2025年第二季度</v>
       </c>
       <c r="H72" s="2"/>
-      <c r="I72" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J72" s="5" t="str">
-        <f t="shared" si="17"/>
-        <v>2024</v>
-      </c>
-      <c r="K72" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>3</v>
+      <c r="I72" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J72" t="str">
+        <f t="shared" si="14"/>
+        <v>2025</v>
+      </c>
+      <c r="K72" t="str">
+        <f t="shared" si="15"/>
+        <v>2</v>
       </c>
       <c r="L72" t="str">
-        <f t="shared" si="9"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="7"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M72" t="str">
-        <f t="shared" si="16"/>
-        <v>君龙人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N72" t="e">
-        <f>COUNTIFS(#REF!,B72)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A73" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="B73" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="C73" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="D73" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="E73" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="F73" s="14" t="s">
-        <v>169</v>
+        <f t="shared" si="13"/>
+        <v>君龙人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>101</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="D73" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E73" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="F73" s="12" t="s">
+        <v>167</v>
       </c>
       <c r="G73" s="2" t="str">
         <f>$J73&amp;"年"&amp;$K73&amp;"季度"</f>
-        <v>2024年3季度</v>
+        <v>2025年2季度</v>
       </c>
       <c r="H73" s="2"/>
-      <c r="I73" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J73" s="5" t="str">
-        <f t="shared" si="17"/>
-        <v>2024</v>
-      </c>
-      <c r="K73" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>3</v>
+      <c r="I73" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J73" t="str">
+        <f t="shared" si="14"/>
+        <v>2025</v>
+      </c>
+      <c r="K73" t="str">
+        <f t="shared" si="15"/>
+        <v>2</v>
       </c>
       <c r="L73" t="str">
-        <f t="shared" si="9"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="7"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M73" t="str">
-        <f t="shared" si="16"/>
-        <v>友邦人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N73" t="e">
-        <f>COUNTIFS(#REF!,B73)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A74" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="B74" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="C74" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="D74" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="E74" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="F74" s="14" t="s">
-        <v>262</v>
+        <f t="shared" si="13"/>
+        <v>友邦人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>101</v>
+      </c>
+      <c r="B74" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="C74" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="D74" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="E74" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="F74" s="12" t="s">
+        <v>249</v>
       </c>
       <c r="G74" s="2" t="str">
         <f>$J74&amp;"年第"&amp;$K74&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H74" s="2"/>
-      <c r="I74" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J74" s="5" t="str">
-        <f t="shared" si="17"/>
-        <v>2024</v>
-      </c>
-      <c r="K74" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>3</v>
+      <c r="I74" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J74" t="str">
+        <f t="shared" si="14"/>
+        <v>2025</v>
+      </c>
+      <c r="K74" t="str">
+        <f t="shared" si="15"/>
+        <v>2</v>
       </c>
       <c r="L74" t="str">
-        <f t="shared" si="9"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="7"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M74" t="str">
-        <f t="shared" si="16"/>
-        <v>中韩人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N74" t="e">
-        <f>COUNTIFS(#REF!,B74)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A75" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="B75" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="C75" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="D75" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="E75" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="F75" s="14" t="s">
-        <v>261</v>
+        <f t="shared" si="13"/>
+        <v>中韩人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>101</v>
+      </c>
+      <c r="B75" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E75" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="F75" s="12" t="s">
+        <v>248</v>
       </c>
       <c r="G75" s="2" t="str">
         <f>$J75&amp;"年第"&amp;$K75&amp;"季度"</f>
-        <v>2024年第3季度</v>
+        <v>2025年第2季度</v>
       </c>
       <c r="H75" s="2"/>
-      <c r="I75" t="str">
-        <f>config!$I$2</f>
-        <v>2024Q3</v>
-      </c>
-      <c r="J75" s="5" t="str">
-        <f t="shared" si="17"/>
-        <v>2024</v>
-      </c>
-      <c r="K75" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>3</v>
+      <c r="I75" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J75" t="str">
+        <f t="shared" si="14"/>
+        <v>2025</v>
+      </c>
+      <c r="K75" t="str">
+        <f t="shared" si="15"/>
+        <v>2</v>
       </c>
       <c r="L75" t="str">
         <f>config!$L$2</f>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M75" t="str">
-        <f t="shared" si="16"/>
-        <v>大家养老2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N75" t="e">
-        <f>COUNTIFS(#REF!,B75)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A76" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="B76" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="D76" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E76" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="F76" s="14" t="s">
-        <v>179</v>
+        <f t="shared" si="13"/>
+        <v>大家养老2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>101</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E76" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="F76" s="12" t="s">
+        <v>176</v>
       </c>
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
-      <c r="I76" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J76" s="5" t="str">
-        <f t="shared" si="17"/>
-        <v>2024</v>
-      </c>
-      <c r="K76" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>3</v>
+      <c r="I76" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J76" t="str">
+        <f t="shared" si="14"/>
+        <v>2025</v>
+      </c>
+      <c r="K76" t="str">
+        <f t="shared" si="15"/>
+        <v>2</v>
       </c>
       <c r="L76" t="str">
-        <f t="shared" si="9"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <f t="shared" si="7"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M76" t="str">
-        <f t="shared" si="16"/>
-        <v>太平人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N76" t="e">
-        <f>COUNTIFS(#REF!,B76)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A77" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="B77" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="C77" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="D77" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E77" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="F77" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="G77" s="7"/>
-      <c r="H77" s="7"/>
-      <c r="I77" t="str">
-        <f>config!$I$2</f>
-        <v>2024Q3</v>
-      </c>
-      <c r="J77" s="5" t="str">
-        <f t="shared" si="17"/>
-        <v>2024</v>
-      </c>
-      <c r="K77" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>3</v>
+        <f t="shared" si="13"/>
+        <v>太平人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>101</v>
+      </c>
+      <c r="B77" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="C77" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D77" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="E77" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="F77" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="G77" s="6"/>
+      <c r="H77" s="6"/>
+      <c r="I77" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J77" t="str">
+        <f t="shared" si="14"/>
+        <v>2025</v>
+      </c>
+      <c r="K77" t="str">
+        <f t="shared" si="15"/>
+        <v>2</v>
       </c>
       <c r="L77" t="str">
         <f>config!$L$2</f>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M77" t="str">
+        <f t="shared" si="13"/>
+        <v>太平养老2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>101</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E78" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F78" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H78" s="6"/>
+      <c r="I78" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J78" t="str">
+        <f t="shared" si="14"/>
+        <v>2025</v>
+      </c>
+      <c r="K78" t="str">
+        <f t="shared" si="15"/>
+        <v>2</v>
+      </c>
+      <c r="L78" t="str">
+        <f t="shared" si="7"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
+      </c>
+      <c r="M78" t="str">
+        <f t="shared" si="13"/>
+        <v>合众人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>101</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E79" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F79" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="G79" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="H79" s="6"/>
+      <c r="I79" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J79" t="str">
+        <f t="shared" ref="J79:J90" si="16">LEFT(I79,4)</f>
+        <v>2025</v>
+      </c>
+      <c r="K79" t="str">
+        <f t="shared" ref="K79:K90" si="17">RIGHT(I79,1)</f>
+        <v>2</v>
+      </c>
+      <c r="L79" t="str">
+        <f t="shared" si="7"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
+      </c>
+      <c r="M79" t="str">
+        <f t="shared" ref="M79:M90" si="18">B79&amp;I79&amp;"偿付能力季度报告摘要.pdf"</f>
+        <v>百年人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>101</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E80" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F80" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="G80" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H80" s="6"/>
+      <c r="I80" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J80" t="str">
         <f t="shared" si="16"/>
-        <v>太平养老2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-      <c r="N77" t="e">
-        <f>COUNTIFS(#REF!,B77)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A78" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="B78" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C78" s="11" t="s">
+        <v>2025</v>
+      </c>
+      <c r="K80" t="str">
+        <f t="shared" si="17"/>
+        <v>2</v>
+      </c>
+      <c r="L80" t="str">
+        <f t="shared" ref="L80:L90" si="19">$L$2</f>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
+      </c>
+      <c r="M80" t="str">
+        <f t="shared" si="18"/>
+        <v>渤海人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>101</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E81" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F81" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="G81" s="6"/>
+      <c r="H81" s="6"/>
+      <c r="I81" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J81" t="str">
+        <f t="shared" si="16"/>
+        <v>2025</v>
+      </c>
+      <c r="K81" t="str">
+        <f t="shared" si="17"/>
+        <v>2</v>
+      </c>
+      <c r="L81" t="str">
+        <f t="shared" si="19"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
+      </c>
+      <c r="M81" t="str">
+        <f t="shared" si="18"/>
+        <v>大家人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>101</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E82" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F82" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="H82" s="6"/>
+      <c r="I82" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J82" t="str">
+        <f t="shared" si="16"/>
+        <v>2025</v>
+      </c>
+      <c r="K82" t="str">
+        <f t="shared" si="17"/>
+        <v>2</v>
+      </c>
+      <c r="L82" t="str">
+        <f t="shared" si="19"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
+      </c>
+      <c r="M82" t="str">
+        <f t="shared" si="18"/>
+        <v>富德生命2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>101</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C83" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="E83" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F83" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="G83" s="6"/>
+      <c r="H83" s="6"/>
+      <c r="I83" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J83" t="str">
+        <f t="shared" si="16"/>
+        <v>2025</v>
+      </c>
+      <c r="K83" t="str">
+        <f t="shared" si="17"/>
+        <v>2</v>
+      </c>
+      <c r="L83" t="str">
+        <f t="shared" si="19"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
+      </c>
+      <c r="M83" t="str">
+        <f t="shared" si="18"/>
+        <v>华夏人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>101</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="E84" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F84" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="G84" s="6"/>
+      <c r="H84" s="6"/>
+      <c r="I84" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J84" t="str">
+        <f t="shared" si="16"/>
+        <v>2025</v>
+      </c>
+      <c r="K84" t="str">
+        <f t="shared" si="17"/>
+        <v>2</v>
+      </c>
+      <c r="L84" t="str">
+        <f t="shared" si="19"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
+      </c>
+      <c r="M84" t="str">
+        <f t="shared" si="18"/>
+        <v>恒大人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>101</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C85" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E85" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="G85" s="6"/>
+      <c r="H85" s="6"/>
+      <c r="I85" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J85" t="str">
+        <f t="shared" si="16"/>
+        <v>2025</v>
+      </c>
+      <c r="K85" t="str">
+        <f t="shared" si="17"/>
+        <v>2</v>
+      </c>
+      <c r="L85" t="str">
+        <f t="shared" si="19"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
+      </c>
+      <c r="M85" t="str">
+        <f t="shared" si="18"/>
+        <v>君康人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>101</v>
+      </c>
+      <c r="B86" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C86" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E86" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F86" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="G86" s="6"/>
+      <c r="H86" s="6"/>
+      <c r="I86" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J86" t="str">
+        <f t="shared" si="16"/>
+        <v>2025</v>
+      </c>
+      <c r="K86" t="str">
+        <f t="shared" si="17"/>
+        <v>2</v>
+      </c>
+      <c r="L86" t="str">
+        <f t="shared" si="19"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
+      </c>
+      <c r="M86" t="str">
+        <f t="shared" si="18"/>
+        <v>前海人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>101</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E87" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F87" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="G87" s="6"/>
+      <c r="H87" s="6"/>
+      <c r="I87" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J87" t="str">
+        <f t="shared" si="16"/>
+        <v>2025</v>
+      </c>
+      <c r="K87" t="str">
+        <f t="shared" si="17"/>
+        <v>2</v>
+      </c>
+      <c r="L87" t="str">
+        <f t="shared" si="19"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
+      </c>
+      <c r="M87" t="str">
+        <f t="shared" si="18"/>
+        <v>上海人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>101</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C88" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="E88" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F88" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G88" s="6"/>
+      <c r="H88" s="6"/>
+      <c r="I88" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J88" t="str">
+        <f t="shared" si="16"/>
+        <v>2025</v>
+      </c>
+      <c r="K88" t="str">
+        <f t="shared" si="17"/>
+        <v>2</v>
+      </c>
+      <c r="L88" t="str">
+        <f t="shared" si="19"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
+      </c>
+      <c r="M88" t="str">
+        <f t="shared" si="18"/>
+        <v>天安人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>101</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E89" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F89" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="G89" s="6"/>
+      <c r="H89" s="6"/>
+      <c r="I89" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J89" t="str">
+        <f t="shared" si="16"/>
+        <v>2025</v>
+      </c>
+      <c r="K89" t="str">
+        <f t="shared" si="17"/>
+        <v>2</v>
+      </c>
+      <c r="L89" t="str">
+        <f t="shared" si="19"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
+      </c>
+      <c r="M89" t="str">
+        <f t="shared" si="18"/>
+        <v>中融人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>101</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C90" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E90" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F90" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="G90" s="6"/>
+      <c r="H90" s="6"/>
+      <c r="I90" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J90" t="str">
+        <f t="shared" si="16"/>
+        <v>2025</v>
+      </c>
+      <c r="K90" t="str">
+        <f t="shared" si="17"/>
+        <v>2</v>
+      </c>
+      <c r="L90" t="str">
+        <f t="shared" si="19"/>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
+      </c>
+      <c r="M90" t="str">
+        <f t="shared" si="18"/>
+        <v>珠江人寿2025Q2偿付能力季度报告摘要.pdf</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>101</v>
+      </c>
+      <c r="B91" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C91" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="D78" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="E78" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="F78" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="G78" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="H78" s="7"/>
-      <c r="I78" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J78" s="5" t="str">
-        <f t="shared" si="17"/>
-        <v>2024</v>
-      </c>
-      <c r="K78" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>3</v>
-      </c>
-      <c r="L78" t="str">
-        <f t="shared" si="9"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
-      </c>
-      <c r="M78" t="str">
-        <f t="shared" si="16"/>
-        <v>合众人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A79" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="B79" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C79" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D79" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="E79" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="F79" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="G79" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="H79" s="7"/>
-      <c r="I79" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J79" s="5" t="str">
-        <f t="shared" ref="J79:J90" si="19">LEFT(I79,4)</f>
-        <v>2024</v>
-      </c>
-      <c r="K79" s="5" t="str">
-        <f t="shared" ref="K79:K90" si="20">RIGHT(I79,1)</f>
-        <v>3</v>
-      </c>
-      <c r="L79" t="str">
-        <f t="shared" si="9"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
-      </c>
-      <c r="M79" t="str">
-        <f t="shared" ref="M79:M90" si="21">B79&amp;I79&amp;"偿付能力季度报告摘要.pdf"</f>
-        <v>百年人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A80" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="B80" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="C80" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D80" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E80" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="F80" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G80" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="H80" s="7"/>
-      <c r="I80" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J80" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>2024</v>
-      </c>
-      <c r="K80" s="5" t="str">
-        <f t="shared" si="20"/>
-        <v>3</v>
-      </c>
-      <c r="L80" t="str">
-        <f t="shared" ref="L80:L90" si="22">$L$2</f>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
-      </c>
-      <c r="M80" t="str">
-        <f t="shared" si="21"/>
-        <v>渤海人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A81" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="B81" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="C81" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D81" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E81" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="F81" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="G81" s="7"/>
-      <c r="H81" s="7"/>
-      <c r="I81" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J81" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>2024</v>
-      </c>
-      <c r="K81" s="5" t="str">
-        <f t="shared" si="20"/>
-        <v>3</v>
-      </c>
-      <c r="L81" t="str">
-        <f t="shared" si="22"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
-      </c>
-      <c r="M81" t="str">
-        <f t="shared" si="21"/>
-        <v>大家人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A82" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="B82" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="C82" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D82" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="E82" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="F82" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="G82" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="H82" s="7"/>
-      <c r="I82" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J82" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>2024</v>
-      </c>
-      <c r="K82" s="5" t="str">
-        <f t="shared" si="20"/>
-        <v>3</v>
-      </c>
-      <c r="L82" t="str">
-        <f t="shared" si="22"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
-      </c>
-      <c r="M82" t="str">
-        <f t="shared" si="21"/>
-        <v>富德生命2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A83" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="B83" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C83" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D83" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="E83" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="F83" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="G83" s="7"/>
-      <c r="H83" s="7"/>
-      <c r="I83" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J83" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>2024</v>
-      </c>
-      <c r="K83" s="5" t="str">
-        <f t="shared" si="20"/>
-        <v>3</v>
-      </c>
-      <c r="L83" t="str">
-        <f t="shared" si="22"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
-      </c>
-      <c r="M83" t="str">
-        <f t="shared" si="21"/>
-        <v>华夏人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A84" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="B84" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C84" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D84" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="E84" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="F84" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="G84" s="7"/>
-      <c r="H84" s="7"/>
-      <c r="I84" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J84" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>2024</v>
-      </c>
-      <c r="K84" s="5" t="str">
-        <f t="shared" si="20"/>
-        <v>3</v>
-      </c>
-      <c r="L84" t="str">
-        <f t="shared" si="22"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
-      </c>
-      <c r="M84" t="str">
-        <f t="shared" si="21"/>
-        <v>恒大人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A85" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="B85" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C85" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D85" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="E85" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="F85" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="G85" s="7"/>
-      <c r="H85" s="7"/>
-      <c r="I85" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J85" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>2024</v>
-      </c>
-      <c r="K85" s="5" t="str">
-        <f t="shared" si="20"/>
-        <v>3</v>
-      </c>
-      <c r="L85" t="str">
-        <f t="shared" si="22"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
-      </c>
-      <c r="M85" t="str">
-        <f t="shared" si="21"/>
-        <v>君康人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A86" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="B86" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C86" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D86" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="E86" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="F86" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="G86" s="7"/>
-      <c r="H86" s="7"/>
-      <c r="I86" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J86" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>2024</v>
-      </c>
-      <c r="K86" s="5" t="str">
-        <f t="shared" si="20"/>
-        <v>3</v>
-      </c>
-      <c r="L86" t="str">
-        <f t="shared" si="22"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
-      </c>
-      <c r="M86" t="str">
-        <f t="shared" si="21"/>
-        <v>前海人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A87" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="B87" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C87" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D87" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E87" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="F87" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="G87" s="7"/>
-      <c r="H87" s="7"/>
-      <c r="I87" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J87" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>2024</v>
-      </c>
-      <c r="K87" s="5" t="str">
-        <f t="shared" si="20"/>
-        <v>3</v>
-      </c>
-      <c r="L87" t="str">
-        <f t="shared" si="22"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
-      </c>
-      <c r="M87" t="str">
-        <f t="shared" si="21"/>
-        <v>上海人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A88" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="B88" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C88" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D88" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="E88" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="F88" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="G88" s="7"/>
-      <c r="H88" s="7"/>
-      <c r="I88" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J88" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>2024</v>
-      </c>
-      <c r="K88" s="5" t="str">
-        <f t="shared" si="20"/>
-        <v>3</v>
-      </c>
-      <c r="L88" t="str">
-        <f t="shared" si="22"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
-      </c>
-      <c r="M88" t="str">
-        <f t="shared" si="21"/>
-        <v>天安人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A89" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="B89" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C89" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D89" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E89" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="F89" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="G89" s="7"/>
-      <c r="H89" s="7"/>
-      <c r="I89" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J89" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>2024</v>
-      </c>
-      <c r="K89" s="5" t="str">
-        <f t="shared" si="20"/>
-        <v>3</v>
-      </c>
-      <c r="L89" t="str">
-        <f t="shared" si="22"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
-      </c>
-      <c r="M89" t="str">
-        <f t="shared" si="21"/>
-        <v>中融人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A90" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="B90" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C90" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D90" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="E90" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="F90" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="G90" s="7"/>
-      <c r="H90" s="7"/>
-      <c r="I90" t="str">
-        <f t="shared" si="10"/>
-        <v>2024Q3</v>
-      </c>
-      <c r="J90" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>2024</v>
-      </c>
-      <c r="K90" s="5" t="str">
-        <f t="shared" si="20"/>
-        <v>3</v>
-      </c>
-      <c r="L90" t="str">
-        <f t="shared" si="22"/>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
-      </c>
-      <c r="M90" t="str">
-        <f t="shared" si="21"/>
-        <v>珠江人寿2024Q3偿付能力季度报告摘要.pdf</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A91" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="B91" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="C91" s="11" t="s">
+      <c r="D91" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="E91" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F91" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D91" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="E91" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="F91" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="G91" s="7"/>
-      <c r="H91" s="7"/>
-      <c r="I91" t="str">
-        <f>config!$I$2</f>
-        <v>2024Q3</v>
-      </c>
-      <c r="J91" s="5" t="str">
+      <c r="G91" s="6"/>
+      <c r="H91" s="6"/>
+      <c r="I91" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J91" t="str">
         <f>LEFT(I91,4)</f>
-        <v>2024</v>
-      </c>
-      <c r="K91" s="5" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K91" t="str">
         <f>RIGHT(I91,1)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L91" t="str">
         <f>config!$L$2</f>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M91" t="str">
         <f>B91&amp;I91&amp;"偿付能力季度报告摘要.pdf"</f>
-        <v>长江养老2024Q3偿付能力季度报告摘要.pdf</v>
+        <v>长江养老2025Q2偿付能力季度报告摘要.pdf</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A92" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="B92" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C92" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="D92" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="E92" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="F92" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="G92" s="7"/>
-      <c r="H92" s="7"/>
-      <c r="I92" t="str">
-        <f>config!$I$2</f>
-        <v>2024Q3</v>
-      </c>
-      <c r="J92" s="5" t="str">
+      <c r="A92" t="s">
+        <v>101</v>
+      </c>
+      <c r="B92" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C92" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="E92" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F92" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="G92" s="6"/>
+      <c r="H92" s="6"/>
+      <c r="I92" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J92" t="str">
         <f>LEFT(I92,4)</f>
-        <v>2024</v>
-      </c>
-      <c r="K92" s="5" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K92" t="str">
         <f>RIGHT(I92,1)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L92" t="str">
         <f>config!$L$2</f>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M92" t="str">
         <f>B92&amp;I92&amp;"偿付能力季度报告摘要.pdf"</f>
-        <v>和谐健康2024Q3偿付能力季度报告摘要.pdf</v>
+        <v>和谐健康2025Q2偿付能力季度报告摘要.pdf</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A93" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="B93" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C93" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="D93" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E93" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="F93" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="G93" s="7"/>
-      <c r="H93" s="7"/>
-      <c r="I93" t="str">
-        <f>config!$I$2</f>
-        <v>2024Q3</v>
-      </c>
-      <c r="J93" s="5" t="str">
+      <c r="A93" t="s">
+        <v>101</v>
+      </c>
+      <c r="B93" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C93" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="D93" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E93" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F93" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="G93" s="6"/>
+      <c r="H93" s="6"/>
+      <c r="I93" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J93" t="str">
         <f>LEFT(I93,4)</f>
-        <v>2024</v>
-      </c>
-      <c r="K93" s="5" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K93" t="str">
         <f>RIGHT(I93,1)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L93" t="str">
         <f>config!$L$2</f>
-        <v>D:\文档\_工作相关\KPMG\CROSS II\2024Q3</v>
+        <v>D:\文档\_工作相关\KPMG\CROSS II\2025Q2</v>
       </c>
       <c r="M93" t="str">
         <f>B93&amp;I93&amp;"偿付能力季度报告摘要.pdf"</f>
-        <v>昆仑健康2024Q3偿付能力季度报告摘要.pdf</v>
+        <v>昆仑健康2025Q2偿付能力季度报告摘要.pdf</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N93"/>
+  <autoFilter ref="A1:N93" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="G1:H44 F78:F90 F76:H76 G77:H1048576 G54:H60 G62:H75">
-    <cfRule type="cellIs" dxfId="12" priority="40" operator="equal">
+  <conditionalFormatting sqref="F73">
+    <cfRule type="cellIs" dxfId="4" priority="37" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F73">
-    <cfRule type="cellIs" dxfId="11" priority="37" operator="equal">
+  <conditionalFormatting sqref="F77:F93">
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G92:H92">
-    <cfRule type="cellIs" dxfId="10" priority="24" operator="equal">
+  <conditionalFormatting sqref="F76:H76">
+    <cfRule type="cellIs" dxfId="2" priority="40" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G93:H93">
-    <cfRule type="cellIs" dxfId="9" priority="23" operator="equal">
+  <conditionalFormatting sqref="G1:H75">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F93">
-    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F91">
-    <cfRule type="cellIs" dxfId="7" priority="10" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F92">
-    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F77">
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G45:H45">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G46:H46">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G47:H47">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G48:H53 H61">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G61">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="G77:H1048576">
+    <cfRule type="cellIs" dxfId="0" priority="23" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="D49" r:id="rId1"/>
+    <hyperlink ref="D49" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
